--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92570910817</v>
+        <v>46157.93107527577</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93107527577</v>
+        <v>46157.93177505738</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93177505738</v>
+        <v>46157.93402361249</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93402361249</v>
+        <v>46157.93720417772</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93720417772</v>
+        <v>46158.28218458587</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28218458587</v>
+        <v>46158.2969153985</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.2969153985</v>
+        <v>46158.29817550754</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29817550754</v>
+        <v>46158.33389486202</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33389486202</v>
+        <v>46158.36859305169</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36859305169</v>
+        <v>46158.37289936684</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
